--- a/backend/data/gmail-test-cases.xlsx
+++ b/backend/data/gmail-test-cases.xlsx
@@ -1269,13 +1269,13 @@
         <v>QA E2E - Starred</v>
       </c>
       <c r="D12" t="str">
-        <v>E2E: Inbox + Starred.</v>
+        <v>E2E: Sent + Starred.</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>INBOX,STARRED</v>
+        <v>SENT,STARRED</v>
       </c>
       <c r="G12" t="str">
         <v>N</v>
@@ -1346,13 +1346,13 @@
         <v>QA E2E - Important</v>
       </c>
       <c r="D13" t="str">
-        <v>E2E: Inbox + Important.</v>
+        <v>E2E: Sent + Important.</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>INBOX,IMPORTANT</v>
+        <v>SENT,IMPORTANT</v>
       </c>
       <c r="G13" t="str">
         <v>N</v>
@@ -3040,7 +3040,7 @@
         <v>QA E2E - In QA-E2E-Staging</v>
       </c>
       <c r="D35" t="str">
-        <v>E2E: staging label + Inbox.</v>
+        <v>E2E: staging label + Sent.</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -3194,7 +3194,7 @@
         <v>QA E2E - In QA-E2E-Compliance</v>
       </c>
       <c r="D37" t="str">
-        <v>E2E: compliance label + Inbox.</v>
+        <v>E2E: compliance label + Sent.</v>
       </c>
       <c r="E37" t="str">
         <v/>

--- a/backend/data/gmail-test-cases.xlsx
+++ b/backend/data/gmail-test-cases.xlsx
@@ -6134,7 +6134,7 @@
         <v>Blockquote and indent format test.</v>
       </c>
       <c r="E75" t="str">
-        <v>&lt;html&gt;&lt;body&gt;&lt;p&gt;Normal paragraph before blockquote.&lt;/p&gt;&lt;blockquote style="margin:0 0 0 40px;border-left:4px solid #ccc;padding-left:8px"&gt;Single level blockquote text.&lt;/blockquote&gt;&lt;blockquote style="margin:0 0 0 40px;border-left:4px solid #ccc;padding-left:8px"&gt;&lt;blockquote style="margin:0 0 0 40px;border-left:4px solid #ccc;padding-left:8px"&gt;Double nested blockquote.&lt;/blockquote&gt;&lt;/blockquote&gt;&lt;p style="padding-left:40px"&gt;Single indent paragraph.&lt;/p&gt;&lt;p style="padding-left:80px"&gt;Double indent paragraph.&lt;/p&gt;&lt;p style="padding-left:120px"&gt;Triple indent paragraph.&lt;/p&gt;&lt;p&gt;Normal paragraph after.&lt;/p&gt;&lt;/body&gt;&lt;/html&gt;</v>
+        <v>&lt;html&gt;&lt;body&gt;&lt;p&gt;Normal paragraph before blockquote. This second sentence is added so the paragraph spans more than a single line.&lt;/p&gt;&lt;blockquote style="margin:0 0 0 40px;border-left:4px solid #ccc;padding-left:8px"&gt;Single level blockquote text. This second sentence keeps the blockquote a real multi-line paragraph.&lt;/blockquote&gt;&lt;blockquote style="margin:0 0 0 40px;border-left:4px solid #ccc;padding-left:8px"&gt;&lt;blockquote style="margin:0 0 0 40px;border-left:4px solid #ccc;padding-left:8px"&gt;Double nested blockquote. This second sentence keeps the nested quote multi-line.&lt;/blockquote&gt;&lt;/blockquote&gt;&lt;p style="padding-left:40px"&gt;Single indent paragraph. This second sentence makes the indented block a real paragraph.&lt;/p&gt;&lt;p style="padding-left:80px"&gt;Double indent paragraph. This second sentence extends the double-indented block.&lt;/p&gt;&lt;p style="padding-left:120px"&gt;Triple indent paragraph. This second sentence extends the triple-indented block.&lt;/p&gt;&lt;p&gt;Normal paragraph after. This second sentence confirms normal flow resumes after the formatted blocks.&lt;/p&gt;&lt;/body&gt;&lt;/html&gt;</v>
       </c>
       <c r="F75" t="str">
         <v>INBOX</v>
